--- a/output/pdf_financials_xlsx/RUCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RUCC.P.xlsx
@@ -479,25 +479,17 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -506,25 +498,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -533,25 +517,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -560,25 +536,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,25 +555,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -614,25 +574,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +593,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,25 +612,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -695,25 +631,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -722,25 +650,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -749,25 +669,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -776,25 +688,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -803,25 +707,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="17">
@@ -830,25 +726,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -911,25 +799,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="21">
@@ -938,25 +818,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -965,25 +837,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -992,25 +856,17 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="24">
@@ -1038,25 +894,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.012</v>
       </c>
     </row>
     <row r="26">
@@ -1065,25 +913,17 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>0.535529</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2.043727</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1.947929</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2.05725</v>
       </c>
     </row>
     <row r="27">
@@ -1092,25 +932,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="28">
@@ -1119,25 +951,17 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1146,25 +970,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="30">
@@ -1200,25 +1016,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1261,25 +1069,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1288,25 +1088,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1315,25 +1107,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1342,25 +1126,17 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1369,25 +1145,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1396,25 +1164,17 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1423,25 +1183,17 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1450,25 +1202,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1477,25 +1221,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1504,25 +1240,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1531,25 +1259,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1558,25 +1278,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1585,25 +1297,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1612,25 +1316,17 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1639,25 +1335,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1693,25 +1381,17 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1720,25 +1400,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1747,25 +1419,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1774,25 +1438,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1801,25 +1457,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1855,25 +1503,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1882,25 +1522,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1909,25 +1541,17 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1936,25 +1560,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1963,25 +1579,17 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1990,25 +1598,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2082,25 +1682,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2109,25 +1701,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2136,25 +1720,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2163,25 +1739,17 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.026231</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.009117</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.016667</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.010055</v>
       </c>
     </row>
     <row r="69">
@@ -2190,25 +1758,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2217,25 +1777,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2244,25 +1796,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2271,25 +1815,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2298,25 +1834,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2325,25 +1853,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2352,25 +1872,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2406,25 +1918,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2433,25 +1937,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2460,25 +1956,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2514,25 +2002,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2541,25 +2021,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2568,25 +2040,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2595,25 +2059,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2622,25 +2078,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2695,25 +2143,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.231628</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.230032</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.230032</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.230032</v>
       </c>
     </row>
     <row r="89">
@@ -2722,25 +2162,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2768,25 +2200,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2814,25 +2238,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2860,25 +2276,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2887,25 +2295,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.223975</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.199898</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.172627</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.14794</v>
       </c>
     </row>
     <row r="97">
@@ -2940,25 +2340,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.054624</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.022481</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.027271</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.024687</v>
       </c>
     </row>
     <row r="100">
@@ -2967,25 +2359,17 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2994,25 +2378,17 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3021,25 +2397,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3048,25 +2416,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3075,25 +2435,17 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.026231</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.017114</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.006612</v>
       </c>
     </row>
     <row r="105">
@@ -3102,25 +2454,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3129,25 +2473,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.022607</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.039595</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.019721</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.031299</v>
       </c>
     </row>
     <row r="107">
@@ -3159,20 +2495,14 @@
       <c r="B107" s="3" t="n">
         <v>0.036</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3181,25 +2511,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3208,25 +2530,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3235,25 +2549,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3262,25 +2568,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3289,25 +2587,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3316,25 +2606,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3343,25 +2625,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3370,25 +2644,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3397,25 +2663,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3424,25 +2682,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3451,25 +2701,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3505,25 +2747,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3532,25 +2766,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3559,25 +2785,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3586,25 +2804,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3613,25 +2823,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3640,25 +2842,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3667,25 +2861,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3721,25 +2907,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.001596</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3794,25 +2972,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3840,25 +3010,17 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.250206</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.209015</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.189294</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.157995</v>
       </c>
     </row>
     <row r="134">
@@ -3867,25 +3029,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4321,7 +3475,11 @@
           <t>Net loss for the period $</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>-0.054624</v>
       </c>
@@ -4351,7 +3509,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.026231</v>
       </c>
@@ -4381,7 +3543,11 @@
           <t>Change in non-cash working capital items total</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.022607</v>
       </c>
@@ -4449,11 +3615,7 @@
           <t>CASH AT THE BEGINNING OF YEAR</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4487,7 +3649,11 @@
           <t>CASH AT THE END OF THE YEAR $</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4551,7 +3717,11 @@
           <t>Share issuance costs</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4623,11 +3793,7 @@
           <t>CASH AT THE BEGINNING OF YEAR</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" s="5" t="n">
         <v>0.134971</v>
       </c>
@@ -4659,7 +3825,11 @@
           <t>CASH AT THE END OF THE YEAR $</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.250206</v>
       </c>
@@ -4761,7 +3931,11 @@
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.015</v>
       </c>
@@ -4991,7 +4165,11 @@
           <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>-0.054624</v>
       </c>

--- a/output/pdf_financials_xlsx/RUCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RUCC.P.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/RUCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RUCC.P.xlsx
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">

--- a/output/pdf_financials_xlsx/RUCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RUCC.P.xlsx
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.250206</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.209015</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.189294</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.157995</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.250206</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.209015</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.189294</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.157995</v>
       </c>
     </row>
     <row r="37">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/RUCC.P.xlsx
+++ b/output/pdf_financials_xlsx/RUCC.P.xlsx
@@ -3978,7 +3978,11 @@
           <t>Shares issued for cash, net (Note 4)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.092628</v>
       </c>
